--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output4.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output4.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S179"/>
+  <dimension ref="A1:T179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,6 +528,11 @@
           <t>Is_Anomaly</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Anomaly_Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -581,13 +586,18 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>4.870296520216211e-05</v>
+        <v>5.027264798837218e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -642,13 +652,18 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>4.870296520216211e-05</v>
+        <v>5.027264798837218e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -703,13 +718,18 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>2.796642524225315e-05</v>
+        <v>4.351827130699516e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -764,13 +784,18 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4.450273641886266e-05</v>
+        <v>7.170770249933938e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -825,13 +850,18 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>5.817626517079128e-05</v>
+        <v>7.335989667509243e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -886,13 +916,18 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>7.343782601400449e-05</v>
+        <v>9.109508792549357e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -947,13 +982,18 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>3.736233084482256e-05</v>
+        <v>4.554752908922667e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1008,13 +1048,18 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>3.821483456779167e-05</v>
+        <v>4.968286497179653e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1069,13 +1114,18 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>5.424443910254866e-05</v>
+        <v>4.37246236486997e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1130,13 +1180,18 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>7.838698377121532e-05</v>
+        <v>6.966131512360054e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1191,13 +1246,18 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>8.048180984634052e-05</v>
+        <v>0.0001011981470732802</v>
       </c>
       <c r="R12" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1252,13 +1312,18 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>7.564129769095231e-05</v>
+        <v>0.0001235862489171995</v>
       </c>
       <c r="R13" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1313,13 +1378,18 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>6.952726077712412e-05</v>
+        <v>7.902766988086954e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1374,13 +1444,18 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>6.952726077712412e-05</v>
+        <v>7.902766988086954e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1435,13 +1510,18 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>6.227300524148486e-05</v>
+        <v>7.762569282605342e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1496,13 +1576,18 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0.000159761463691173</v>
+        <v>0.0001055144282787217</v>
       </c>
       <c r="R17" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1557,13 +1642,18 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>8.420146538045482e-05</v>
+        <v>0.000104246018070268</v>
       </c>
       <c r="R18" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1618,13 +1708,18 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>7.025193151713486e-05</v>
+        <v>9.952065913361688e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1679,13 +1774,18 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>7.025193151713486e-05</v>
+        <v>9.952065913361688e-05</v>
       </c>
       <c r="R20" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1740,13 +1840,18 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>6.473628194802633e-05</v>
+        <v>4.873125243170577e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1801,13 +1906,18 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>7.765538442768179e-05</v>
+        <v>7.017472587353251e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1862,13 +1972,18 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>7.765538442768179e-05</v>
+        <v>7.017472587353251e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1923,13 +2038,18 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>0.0003064587366631033</v>
+        <v>0.0002089911757788066</v>
       </c>
       <c r="R24" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1984,13 +2104,18 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>6.789845734325586e-05</v>
+        <v>7.690829613836289e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2045,13 +2170,18 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>5.808605398603022e-05</v>
+        <v>5.138670428556134e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2106,13 +2236,18 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>8.216435115746856e-05</v>
+        <v>3.942966305649375e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2167,13 +2302,18 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>7.804842230274567e-05</v>
+        <v>4.380589187936435e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2228,13 +2368,18 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>6.105894167014037e-05</v>
+        <v>5.815254061476176e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2289,13 +2434,18 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>7.364096837763725e-05</v>
+        <v>7.171824679838021e-05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2350,13 +2500,18 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>6.483232502271202e-05</v>
+        <v>5.580348476542091e-05</v>
       </c>
       <c r="R31" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2411,13 +2566,18 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>7.353292415764051e-05</v>
+        <v>2.515002246578608e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2472,13 +2632,18 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>7.353292415764051e-05</v>
+        <v>2.515002246578608e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2533,13 +2698,18 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>6.054194194864791e-05</v>
+        <v>4.34265435066245e-05</v>
       </c>
       <c r="R34" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2594,13 +2764,18 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>8.454580456676863e-05</v>
+        <v>5.815458629139708e-05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2655,13 +2830,18 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>6.756309053889424e-05</v>
+        <v>0.0001099160403515182</v>
       </c>
       <c r="R36" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2716,13 +2896,18 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>5.271313805726911e-05</v>
+        <v>5.28525278925585e-05</v>
       </c>
       <c r="R37" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2777,13 +2962,18 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>5.312808725902522e-05</v>
+        <v>4.52423534968162e-05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2838,13 +3028,18 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>5.312840319820959e-05</v>
+        <v>4.524200521616989e-05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2899,13 +3094,18 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>8.312991866580663e-05</v>
+        <v>4.388278746952911e-05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2960,13 +3160,18 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>0.0001073346950476159</v>
+        <v>4.410800496607345e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3021,13 +3226,18 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>0.000151163906431101</v>
+        <v>0.0001227135373296639</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3082,13 +3292,18 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>5.447131195782578e-05</v>
+        <v>4.045413803249573e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3143,13 +3358,18 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>5.447131195782578e-05</v>
+        <v>4.045413803249573e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3204,13 +3424,18 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>6.313349380916499e-05</v>
+        <v>3.166668048284988e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3265,13 +3490,18 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>7.971934068940633e-05</v>
+        <v>5.768743460831236e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3326,13 +3556,18 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>6.947081633594123e-05</v>
+        <v>4.562670775320256e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3387,13 +3622,18 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>6.947081633594123e-05</v>
+        <v>4.562670775320256e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3448,13 +3688,18 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>5.901239665246733e-05</v>
+        <v>7.757143306649896e-05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3509,13 +3754,18 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>6.41959785963885e-05</v>
+        <v>4.942407857532895e-05</v>
       </c>
       <c r="R50" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3570,13 +3820,18 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>6.41959785963885e-05</v>
+        <v>4.942407857532895e-05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3631,13 +3886,18 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>9.141723652476429e-05</v>
+        <v>4.036463187133991e-05</v>
       </c>
       <c r="R52" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3692,13 +3952,18 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>7.361426990528428e-05</v>
+        <v>5.413460214199117e-05</v>
       </c>
       <c r="R53" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3753,13 +4018,18 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>5.730796139664611e-05</v>
+        <v>7.086268923832172e-05</v>
       </c>
       <c r="R54" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3814,13 +4084,18 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>0.0005415612519096343</v>
+        <v>0.0001053868401501588</v>
       </c>
       <c r="R55" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3875,13 +4150,18 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>5.083161159426644e-05</v>
+        <v>4.398599805319043e-05</v>
       </c>
       <c r="R56" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3936,13 +4216,18 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>4.449098253679177e-05</v>
+        <v>4.577466300157347e-05</v>
       </c>
       <c r="R57" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3997,13 +4282,18 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>3.141556933476423e-05</v>
+        <v>4.823941922375837e-05</v>
       </c>
       <c r="R58" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4058,13 +4348,18 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>4.204005887603665e-05</v>
+        <v>5.349471582463834e-05</v>
       </c>
       <c r="R59" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4119,13 +4414,18 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>4.204005887603665e-05</v>
+        <v>5.349471582463834e-05</v>
       </c>
       <c r="R60" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4180,13 +4480,18 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>5.747591753067161e-05</v>
+        <v>7.633256204444698e-05</v>
       </c>
       <c r="R61" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -4241,13 +4546,18 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>7.092396679773436e-05</v>
+        <v>5.964298220349685e-05</v>
       </c>
       <c r="R62" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -4302,13 +4612,18 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>6.252753791112767e-05</v>
+        <v>5.171415153579421e-05</v>
       </c>
       <c r="R63" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4363,13 +4678,18 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>3.49485148020687e-05</v>
+        <v>5.565967784292134e-05</v>
       </c>
       <c r="R64" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4424,13 +4744,18 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>7.1853610387252e-05</v>
+        <v>0.0001053187229771056</v>
       </c>
       <c r="R65" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4485,13 +4810,18 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>4.477414549115278e-05</v>
+        <v>7.615067355124229e-05</v>
       </c>
       <c r="R66" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4546,13 +4876,18 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>4.85573080513889e-05</v>
+        <v>6.321357248457284e-05</v>
       </c>
       <c r="R67" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4607,13 +4942,18 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>5.366653474536895e-05</v>
+        <v>4.065007785964516e-05</v>
       </c>
       <c r="R68" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4668,13 +5008,18 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>6.967916861797223e-05</v>
+        <v>4.467392658952362e-05</v>
       </c>
       <c r="R69" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4729,13 +5074,18 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>0.0001456502616469604</v>
+        <v>7.397659802732492e-05</v>
       </c>
       <c r="R70" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4790,13 +5140,18 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>0.0001456507549573778</v>
+        <v>7.397652881620802e-05</v>
       </c>
       <c r="R71" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4851,13 +5206,18 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>6.356574507861741e-05</v>
+        <v>6.430886188354284e-05</v>
       </c>
       <c r="R72" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4912,13 +5272,18 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>7.754813601896092e-05</v>
+        <v>6.270653133888267e-05</v>
       </c>
       <c r="R73" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4973,13 +5338,18 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>4.177142601307024e-05</v>
+        <v>4.276091523389266e-05</v>
       </c>
       <c r="R74" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -5034,13 +5404,18 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>7.358208919060892e-05</v>
+        <v>4.480216101664095e-05</v>
       </c>
       <c r="R75" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -5095,13 +5470,18 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>0.008213239833446186</v>
+        <v>0.0009133740973889834</v>
       </c>
       <c r="R76" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S76" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5156,13 +5536,18 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>8.523188076363922e-05</v>
+        <v>6.892733845505222e-05</v>
       </c>
       <c r="R77" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -5217,13 +5602,18 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>4.798303041531982e-05</v>
+        <v>6.298335584170424e-05</v>
       </c>
       <c r="R78" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -5278,13 +5668,18 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>3.954922227088435e-05</v>
+        <v>5.464773786201401e-05</v>
       </c>
       <c r="R79" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -5339,13 +5734,18 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>4.625723148463087e-05</v>
+        <v>5.739358309762761e-05</v>
       </c>
       <c r="R80" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -5400,13 +5800,18 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>5.343131279314367e-05</v>
+        <v>4.413022877420414e-05</v>
       </c>
       <c r="R81" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -5461,13 +5866,18 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>3.621498027906477e-05</v>
+        <v>4.353862742825502e-05</v>
       </c>
       <c r="R82" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -5522,13 +5932,18 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>2.82874576244185e-05</v>
+        <v>4.770290527650615e-05</v>
       </c>
       <c r="R83" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -5583,13 +5998,18 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>4.209846425930394e-05</v>
+        <v>5.881955703682367e-05</v>
       </c>
       <c r="R84" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5644,13 +6064,18 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>4.262230895505165e-05</v>
+        <v>4.563837886858323e-05</v>
       </c>
       <c r="R85" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5705,13 +6130,18 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>4.262230895505165e-05</v>
+        <v>4.563837886858323e-05</v>
       </c>
       <c r="R86" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5766,13 +6196,18 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>6.225236189592985e-05</v>
+        <v>4.505763972131403e-05</v>
       </c>
       <c r="R87" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5827,13 +6262,18 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0.000318637460900952</v>
+        <v>0.0002035971611857493</v>
       </c>
       <c r="R88" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5888,13 +6328,18 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>0.0001281936273151277</v>
+        <v>0.0001131798122710701</v>
       </c>
       <c r="R89" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5949,13 +6394,18 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>5.658245001100403e-05</v>
+        <v>8.610664013168935e-05</v>
       </c>
       <c r="R90" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -6010,13 +6460,18 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>5.638042851648783e-05</v>
+        <v>7.895065209030013e-05</v>
       </c>
       <c r="R91" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -6071,13 +6526,18 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>6.111729004932057e-05</v>
+        <v>7.175261154370145e-05</v>
       </c>
       <c r="R92" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -6132,13 +6592,18 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>5.281620249787087e-05</v>
+        <v>3.521339190377608e-05</v>
       </c>
       <c r="R93" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -6193,13 +6658,18 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>7.749792374052143e-05</v>
+        <v>5.283560924847845e-05</v>
       </c>
       <c r="R94" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -6254,13 +6724,18 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>9.129130820829832e-05</v>
+        <v>6.398507666779496e-05</v>
       </c>
       <c r="R95" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -6315,13 +6790,18 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>0.0001066175728893593</v>
+        <v>6.032185242874403e-05</v>
       </c>
       <c r="R96" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -6376,13 +6856,18 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>7.546066622654737e-05</v>
+        <v>4.813551265934783e-05</v>
       </c>
       <c r="R97" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -6437,13 +6922,18 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>7.546066622654737e-05</v>
+        <v>4.813551265934783e-05</v>
       </c>
       <c r="R98" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -6498,13 +6988,18 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>3.565919131721337e-05</v>
+        <v>3.765009567110047e-05</v>
       </c>
       <c r="R99" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -6559,13 +7054,18 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>8.077551484081157e-05</v>
+        <v>6.031148997951918e-05</v>
       </c>
       <c r="R100" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -6620,13 +7120,18 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>7.265082816938475e-05</v>
+        <v>5.898912302303628e-05</v>
       </c>
       <c r="R101" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -6681,13 +7186,18 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>5.47130113567209e-05</v>
+        <v>6.308636188290636e-05</v>
       </c>
       <c r="R102" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -6742,13 +7252,18 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>3.327978685478366e-05</v>
+        <v>3.25937832939078e-05</v>
       </c>
       <c r="R103" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -6803,13 +7318,18 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>4.644668136451105e-05</v>
+        <v>4.025647439461994e-05</v>
       </c>
       <c r="R104" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -6864,13 +7384,18 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>0.0001329317816520778</v>
+        <v>5.086285607663974e-05</v>
       </c>
       <c r="R105" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -6925,13 +7450,18 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>0.0002105229716003802</v>
+        <v>5.361635200619546e-05</v>
       </c>
       <c r="R106" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -6986,13 +7516,18 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>0.0002372517834460483</v>
+        <v>8.796492928534685e-05</v>
       </c>
       <c r="R107" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -7047,13 +7582,18 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>0.0001275913620969875</v>
+        <v>0.000109061046840753</v>
       </c>
       <c r="R108" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -7108,13 +7648,18 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>4.118827454775794e-05</v>
+        <v>5.381085929856091e-05</v>
       </c>
       <c r="R109" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -7169,13 +7714,18 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>4.953781447281302e-05</v>
+        <v>4.718480638698533e-05</v>
       </c>
       <c r="R110" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -7230,13 +7780,18 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>9.800515455203092e-05</v>
+        <v>5.006117756097003e-05</v>
       </c>
       <c r="R111" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -7291,13 +7846,18 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>7.423035635496702e-05</v>
+        <v>9.102126286026025e-05</v>
       </c>
       <c r="R112" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -7352,13 +7912,18 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>7.423035635496702e-05</v>
+        <v>9.102126286026025e-05</v>
       </c>
       <c r="R113" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -7413,13 +7978,18 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>8.961704538843049e-05</v>
+        <v>8.420216558054727e-05</v>
       </c>
       <c r="R114" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -7474,13 +8044,18 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>8.682894742227506e-05</v>
+        <v>8.143596759787999e-05</v>
       </c>
       <c r="R115" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -7535,13 +8110,18 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>5.170213199564381e-05</v>
+        <v>5.638394076867358e-05</v>
       </c>
       <c r="R116" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -7596,13 +8176,18 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>7.075825910916461e-05</v>
+        <v>4.288311597334154e-05</v>
       </c>
       <c r="R117" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -7657,13 +8242,18 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>7.809859281432334e-05</v>
+        <v>4.219475010183002e-05</v>
       </c>
       <c r="R118" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -7718,13 +8308,18 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0.0001249465935330357</v>
+        <v>5.510556497067327e-05</v>
       </c>
       <c r="R119" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -7779,13 +8374,18 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>0.004828348458052151</v>
+        <v>0.001118620023890901</v>
       </c>
       <c r="R120" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S120" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -7840,13 +8440,18 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>4.579226071051804e-05</v>
+        <v>5.563293889636511e-05</v>
       </c>
       <c r="R121" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -7901,13 +8506,18 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>4.579226071051804e-05</v>
+        <v>5.563293889636511e-05</v>
       </c>
       <c r="R122" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -7962,13 +8572,18 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>8.452259786224937e-05</v>
+        <v>5.679779963910266e-05</v>
       </c>
       <c r="R123" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -8023,13 +8638,18 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>7.690800032058068e-05</v>
+        <v>6.50328033649133e-05</v>
       </c>
       <c r="R124" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -8084,13 +8704,18 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>8.959426387537996e-05</v>
+        <v>7.354666188407584e-05</v>
       </c>
       <c r="R125" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -8145,13 +8770,18 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>0.003322937047948653</v>
+        <v>0.001083665509022183</v>
       </c>
       <c r="R126" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -8206,13 +8836,18 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>8.966686028368521e-05</v>
+        <v>6.290184563290585e-05</v>
       </c>
       <c r="R127" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -8267,13 +8902,18 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>7.8778831369412e-05</v>
+        <v>4.625794754378257e-05</v>
       </c>
       <c r="R128" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -8328,13 +8968,18 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>0.0001223671534562511</v>
+        <v>4.784601037275509e-05</v>
       </c>
       <c r="R129" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -8389,13 +9034,18 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>0.0001073673383507787</v>
+        <v>6.329260765730288e-05</v>
       </c>
       <c r="R130" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -8450,13 +9100,18 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>3.664556506317757e-05</v>
+        <v>6.04407600281573e-05</v>
       </c>
       <c r="R131" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -8511,13 +9166,18 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>3.590471258085422e-05</v>
+        <v>5.35921199285556e-05</v>
       </c>
       <c r="R132" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -8572,13 +9232,18 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>8.249587317392848e-05</v>
+        <v>4.022084030433136e-05</v>
       </c>
       <c r="R133" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -8633,13 +9298,18 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>6.597555156383745e-05</v>
+        <v>4.918131052440579e-05</v>
       </c>
       <c r="R134" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -8694,13 +9364,18 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>6.612786772340623e-05</v>
+        <v>6.966449085870265e-05</v>
       </c>
       <c r="R135" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -8755,13 +9430,18 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>0.0001050546765129013</v>
+        <v>0.0001322188005229374</v>
       </c>
       <c r="R136" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -8816,13 +9496,18 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>0.0001050546616409521</v>
+        <v>0.0001322189008228614</v>
       </c>
       <c r="R137" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -8877,13 +9562,18 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>0.0003411846456840056</v>
+        <v>0.0001395185846263821</v>
       </c>
       <c r="R138" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -8938,13 +9628,18 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>6.575138226788315e-05</v>
+        <v>5.170332595135556e-05</v>
       </c>
       <c r="R139" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -8999,13 +9694,18 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>4.082339148616874e-05</v>
+        <v>4.70454089341509e-05</v>
       </c>
       <c r="R140" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -9060,13 +9760,18 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>3.396176272721512e-05</v>
+        <v>4.594125453302378e-05</v>
       </c>
       <c r="R141" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -9121,13 +9826,18 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>8.890417519598921e-05</v>
+        <v>8.905868525094072e-05</v>
       </c>
       <c r="R142" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -9182,13 +9892,18 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>4.775657200692313e-05</v>
+        <v>5.214442400949391e-05</v>
       </c>
       <c r="R143" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -9243,13 +9958,18 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>4.11094822450605e-05</v>
+        <v>3.858277014037711e-05</v>
       </c>
       <c r="R144" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -9304,13 +10024,18 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>7.335234943663016e-05</v>
+        <v>3.606872213977026e-05</v>
       </c>
       <c r="R145" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -9365,13 +10090,18 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>0.0003073561410181009</v>
+        <v>0.0002340896565340206</v>
       </c>
       <c r="R146" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -9426,13 +10156,18 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>4.545821872044923e-05</v>
+        <v>6.986096655577747e-05</v>
       </c>
       <c r="R147" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -9487,13 +10222,18 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>0.002624353172805802</v>
+        <v>0.0004945996059425025</v>
       </c>
       <c r="R148" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -9548,13 +10288,18 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>4.324425535663472e-05</v>
+        <v>4.395620262604091e-05</v>
       </c>
       <c r="R149" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -9609,13 +10354,18 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>4.90144423242533e-05</v>
+        <v>4.505920117770916e-05</v>
       </c>
       <c r="R150" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -9670,13 +10420,18 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>6.150879778228351e-05</v>
+        <v>5.066270293992815e-05</v>
       </c>
       <c r="R151" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S151" t="b">
         <v>0</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -9731,13 +10486,18 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>5.046899912116728e-05</v>
+        <v>6.858897867630342e-05</v>
       </c>
       <c r="R152" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S152" t="b">
         <v>0</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -9792,13 +10552,18 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>5.046899912116728e-05</v>
+        <v>6.858897867630342e-05</v>
       </c>
       <c r="R153" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S153" t="b">
         <v>0</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -9853,13 +10618,18 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>8.186074369753164e-05</v>
+        <v>6.669814277677595e-05</v>
       </c>
       <c r="R154" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S154" t="b">
         <v>0</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -9914,13 +10684,18 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>5.205817712128859e-05</v>
+        <v>3.742055903389135e-05</v>
       </c>
       <c r="R155" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S155" t="b">
         <v>0</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -9975,13 +10750,18 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>5.205817712128859e-05</v>
+        <v>3.742055903389135e-05</v>
       </c>
       <c r="R156" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S156" t="b">
         <v>0</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -10036,13 +10816,18 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>5.899342747892292e-05</v>
+        <v>4.816820610764867e-05</v>
       </c>
       <c r="R157" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S157" t="b">
         <v>0</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -10097,13 +10882,18 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>5.286712408830297e-05</v>
+        <v>5.529906265315145e-05</v>
       </c>
       <c r="R158" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S158" t="b">
         <v>0</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -10158,13 +10948,18 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>4.551925223735508e-05</v>
+        <v>0.0001056579636192658</v>
       </c>
       <c r="R159" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S159" t="b">
         <v>0</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -10219,13 +11014,18 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>8.308027354711948e-05</v>
+        <v>6.593808698521568e-05</v>
       </c>
       <c r="R160" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S160" t="b">
         <v>0</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -10280,13 +11080,18 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>0.0001301481972105227</v>
+        <v>8.123811156771939e-05</v>
       </c>
       <c r="R161" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S161" t="b">
         <v>0</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -10341,13 +11146,18 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>9.534869209080754e-05</v>
+        <v>4.359954016990005e-05</v>
       </c>
       <c r="R162" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S162" t="b">
         <v>0</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -10402,13 +11212,18 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>4.795531367042503e-05</v>
+        <v>4.059409246797011e-05</v>
       </c>
       <c r="R163" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S163" t="b">
         <v>0</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -10463,13 +11278,18 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>5.06518319488702e-05</v>
+        <v>6.622397875766242e-05</v>
       </c>
       <c r="R164" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S164" t="b">
         <v>0</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -10524,13 +11344,18 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>7.910922033658671e-05</v>
+        <v>7.330114779857821e-05</v>
       </c>
       <c r="R165" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S165" t="b">
         <v>0</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -10585,13 +11410,18 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>7.320197616662269e-05</v>
+        <v>5.925373271692334e-05</v>
       </c>
       <c r="R166" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S166" t="b">
         <v>0</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -10646,13 +11476,18 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>9.318917798520756e-05</v>
+        <v>4.553185994015261e-05</v>
       </c>
       <c r="R167" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S167" t="b">
         <v>0</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -10707,13 +11542,18 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>5.847825432739429e-05</v>
+        <v>3.746019863799699e-05</v>
       </c>
       <c r="R168" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S168" t="b">
         <v>0</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -10768,13 +11608,18 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>6.226440043626501e-05</v>
+        <v>3.996272641605609e-05</v>
       </c>
       <c r="R169" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S169" t="b">
         <v>0</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -10829,13 +11674,18 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>4.610865760214553e-05</v>
+        <v>5.699185257119693e-05</v>
       </c>
       <c r="R170" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S170" t="b">
         <v>0</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -10890,13 +11740,18 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>6.764418450184425e-05</v>
+        <v>5.530020963111133e-05</v>
       </c>
       <c r="R171" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S171" t="b">
         <v>0</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -10951,13 +11806,18 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>7.453598887501733e-05</v>
+        <v>7.005168487261875e-05</v>
       </c>
       <c r="R172" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S172" t="b">
         <v>0</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -11012,13 +11872,18 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>5.542497604542309e-05</v>
+        <v>4.518545126879049e-05</v>
       </c>
       <c r="R173" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S173" t="b">
         <v>0</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -11073,13 +11938,18 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>5.386470064105343e-05</v>
+        <v>3.708314994178098e-05</v>
       </c>
       <c r="R174" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S174" t="b">
         <v>0</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -11134,13 +12004,18 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>5.453365070006751e-05</v>
+        <v>4.696668769862695e-05</v>
       </c>
       <c r="R175" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S175" t="b">
         <v>0</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -11195,13 +12070,18 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>8.600795478223062e-05</v>
+        <v>5.817082549717244e-05</v>
       </c>
       <c r="R176" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S176" t="b">
         <v>0</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -11256,13 +12136,18 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>8.600795478223062e-05</v>
+        <v>5.817082549717244e-05</v>
       </c>
       <c r="R177" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S177" t="b">
         <v>0</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -11317,13 +12202,18 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>8.998851179114225e-05</v>
+        <v>0.0001128604777223931</v>
       </c>
       <c r="R178" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S178" t="b">
         <v>0</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -11378,13 +12268,18 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>8.587226922700806e-05</v>
+        <v>6.44159073169705e-05</v>
       </c>
       <c r="R179" t="n">
-        <v>0.003337332539515998</v>
+        <v>0.001352842468665255</v>
       </c>
       <c r="S179" t="b">
         <v>0</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output4.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output4.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>5.027264798837218e-05</v>
+        <v>2.735325589785399e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>5.027264798837218e-05</v>
+        <v>2.735325589785399e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>4.351827130699516e-05</v>
+        <v>8.261949800542362e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>7.170770249933938e-05</v>
+        <v>3.58069271663416e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>7.335989667509243e-05</v>
+        <v>3.208811668888072e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>9.109508792549357e-05</v>
+        <v>6.087732764045651e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>4.554752908922667e-05</v>
+        <v>1.48623691850096e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>4.968286497179653e-05</v>
+        <v>1.655907688176896e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>4.37246236486997e-05</v>
+        <v>2.034317079569504e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>6.966131512360054e-05</v>
+        <v>1.944159385147585e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001011981470732802</v>
+        <v>4.964634294744504e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001235862489171995</v>
+        <v>6.286658213720738e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>7.902766988086954e-05</v>
+        <v>4.471755847809748e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>7.902766988086954e-05</v>
+        <v>4.471755847809748e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>7.762569282605342e-05</v>
+        <v>6.149128510496237e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001055144282787217</v>
+        <v>0.0001244501419282848</v>
       </c>
       <c r="R17" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>0.000104246018070268</v>
+        <v>5.24303274756275e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>9.952065913361688e-05</v>
+        <v>5.234189478213816e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>9.952065913361688e-05</v>
+        <v>5.234189478213816e-05</v>
       </c>
       <c r="R20" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>4.873125243170577e-05</v>
+        <v>3.567608391161504e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>7.017472587353251e-05</v>
+        <v>4.890116861362313e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>7.017472587353251e-05</v>
+        <v>4.890116861362313e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>0.0002089911757788066</v>
+        <v>0.000236276169721859</v>
       </c>
       <c r="R24" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>7.690829613836289e-05</v>
+        <v>4.566268192947868e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>5.138670428556134e-05</v>
+        <v>3.12742559178432e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>3.942966305649375e-05</v>
+        <v>5.376592420598126e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>4.380589187936435e-05</v>
+        <v>5.123101639563925e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>5.815254061476176e-05</v>
+        <v>1.434228785019277e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>7.171824679838021e-05</v>
+        <v>1.959485734992831e-05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>5.580348476542091e-05</v>
+        <v>3.796128121459404e-05</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>2.515002246578608e-05</v>
+        <v>4.476896260395484e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>2.515002246578608e-05</v>
+        <v>4.476896260395484e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>4.34265435066245e-05</v>
+        <v>3.74592625458033e-05</v>
       </c>
       <c r="R34" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>5.815458629139708e-05</v>
+        <v>4.320490917840709e-05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>0.0001099160403515182</v>
+        <v>5.280855592180853e-05</v>
       </c>
       <c r="R36" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>5.28525278925585e-05</v>
+        <v>2.710882036905469e-05</v>
       </c>
       <c r="R37" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>4.52423534968162e-05</v>
+        <v>2.402524004685782e-05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>4.524200521616989e-05</v>
+        <v>2.402547698932341e-05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>4.388278746952911e-05</v>
+        <v>5.970522484807202e-05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>4.410800496607345e-05</v>
+        <v>5.34469946914323e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>0.0001227135373296639</v>
+        <v>0.0001255857492984235</v>
       </c>
       <c r="R42" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>4.045413803249573e-05</v>
+        <v>3.00689252810606e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>4.045413803249573e-05</v>
+        <v>3.00689252810606e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>3.166668048284988e-05</v>
+        <v>3.311866955292688e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>5.768743460831236e-05</v>
+        <v>6.626386017046919e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>4.562670775320256e-05</v>
+        <v>4.966763040617445e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>4.562670775320256e-05</v>
+        <v>4.966763040617445e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>7.757143306649896e-05</v>
+        <v>3.862124474042327e-05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>4.942407857532895e-05</v>
+        <v>3.616218945361854e-05</v>
       </c>
       <c r="R50" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>4.942407857532895e-05</v>
+        <v>3.616218945361854e-05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>4.036463187133991e-05</v>
+        <v>5.099579949508803e-05</v>
       </c>
       <c r="R52" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>5.413460214199117e-05</v>
+        <v>1.971017561102317e-05</v>
       </c>
       <c r="R53" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>7.086268923832172e-05</v>
+        <v>3.218044982100451e-05</v>
       </c>
       <c r="R54" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>0.0001053868401501588</v>
+        <v>0.0004059028710697949</v>
       </c>
       <c r="R55" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>4.398599805319043e-05</v>
+        <v>2.64432500304668e-05</v>
       </c>
       <c r="R56" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>4.577466300157347e-05</v>
+        <v>2.083824626511248e-05</v>
       </c>
       <c r="R57" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>4.823941922375837e-05</v>
+        <v>7.293121364630753e-06</v>
       </c>
       <c r="R58" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>5.349471582463834e-05</v>
+        <v>8.661617314960431e-06</v>
       </c>
       <c r="R59" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>5.349471582463834e-05</v>
+        <v>8.661617314960431e-06</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>7.633256204444698e-05</v>
+        <v>3.613977285370048e-05</v>
       </c>
       <c r="R61" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>5.964298220349685e-05</v>
+        <v>4.346805334000133e-05</v>
       </c>
       <c r="R62" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>5.171415153579421e-05</v>
+        <v>3.553672623713132e-05</v>
       </c>
       <c r="R63" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>5.565967784292134e-05</v>
+        <v>3.920162150716836e-06</v>
       </c>
       <c r="R64" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>0.0001053187229771056</v>
+        <v>4.741075125373525e-05</v>
       </c>
       <c r="R65" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>7.615067355124229e-05</v>
+        <v>3.124941664333555e-05</v>
       </c>
       <c r="R66" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>6.321357248457284e-05</v>
+        <v>2.521460926764326e-05</v>
       </c>
       <c r="R67" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>4.065007785964516e-05</v>
+        <v>3.327667174599972e-05</v>
       </c>
       <c r="R68" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>4.467392658952362e-05</v>
+        <v>4.384854780681308e-05</v>
       </c>
       <c r="R69" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>7.397659802732492e-05</v>
+        <v>0.0001167218226335836</v>
       </c>
       <c r="R70" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>7.397652881620802e-05</v>
+        <v>0.0001167217525352669</v>
       </c>
       <c r="R71" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>6.430886188354284e-05</v>
+        <v>2.946883245525381e-05</v>
       </c>
       <c r="R72" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>6.270653133888267e-05</v>
+        <v>7.533785622109846e-05</v>
       </c>
       <c r="R73" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5338,10 +5338,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>4.276091523389266e-05</v>
+        <v>2.292993665836495e-05</v>
       </c>
       <c r="R74" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>4.480216101664095e-05</v>
+        <v>5.048397339408269e-05</v>
       </c>
       <c r="R75" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>0.0009133740973889834</v>
+        <v>0.004992620239977628</v>
       </c>
       <c r="R76" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>6.892733845505222e-05</v>
+        <v>5.363428989485576e-05</v>
       </c>
       <c r="R77" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>6.298335584170424e-05</v>
+        <v>2.037350048401155e-05</v>
       </c>
       <c r="R78" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>5.464773786201401e-05</v>
+        <v>1.928558554142768e-05</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>5.739358309762761e-05</v>
+        <v>2.126978759899165e-05</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>4.413022877420414e-05</v>
+        <v>1.972285138000443e-05</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>4.353862742825502e-05</v>
+        <v>1.220153669908726e-05</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>4.770290527650615e-05</v>
+        <v>1.625415427173539e-05</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>5.881955703682367e-05</v>
+        <v>2.117682636448642e-05</v>
       </c>
       <c r="R84" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>4.563837886858323e-05</v>
+        <v>1.806317671530174e-05</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>4.563837886858323e-05</v>
+        <v>1.806317671530174e-05</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>4.505763972131403e-05</v>
+        <v>3.658298667483492e-05</v>
       </c>
       <c r="R87" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6262,10 +6262,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0.0002035971611857493</v>
+        <v>0.0002418021623573908</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>0.0001131798122710701</v>
+        <v>0.000107653359474629</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>8.610664013168935e-05</v>
+        <v>3.91818920761711e-05</v>
       </c>
       <c r="R90" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>7.895065209030013e-05</v>
+        <v>3.014665029395538e-05</v>
       </c>
       <c r="R91" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>7.175261154370145e-05</v>
+        <v>4.313789462139902e-05</v>
       </c>
       <c r="R92" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>3.521339190377608e-05</v>
+        <v>2.32936625165187e-05</v>
       </c>
       <c r="R93" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>5.283560924847845e-05</v>
+        <v>7.004149725963972e-05</v>
       </c>
       <c r="R94" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>6.398507666779496e-05</v>
+        <v>9.094349811068723e-05</v>
       </c>
       <c r="R95" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>6.032185242874403e-05</v>
+        <v>9.982290160717594e-05</v>
       </c>
       <c r="R96" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>4.813551265934783e-05</v>
+        <v>6.062810994130219e-05</v>
       </c>
       <c r="R97" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>4.813551265934783e-05</v>
+        <v>6.062810994130219e-05</v>
       </c>
       <c r="R98" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>3.765009567110047e-05</v>
+        <v>2.16043303650265e-05</v>
       </c>
       <c r="R99" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>6.031148997951918e-05</v>
+        <v>7.617526913504183e-05</v>
       </c>
       <c r="R100" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>5.898912302303628e-05</v>
+        <v>6.433675635382179e-05</v>
       </c>
       <c r="R101" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>6.308636188290636e-05</v>
+        <v>4.272756945323168e-05</v>
       </c>
       <c r="R102" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>3.25937832939078e-05</v>
+        <v>1.578289510386826e-05</v>
       </c>
       <c r="R103" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>4.025647439461994e-05</v>
+        <v>3.429611095913747e-05</v>
       </c>
       <c r="R104" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>5.086285607663974e-05</v>
+        <v>0.0001256930277602476</v>
       </c>
       <c r="R105" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>5.361635200619546e-05</v>
+        <v>0.0002197419099503587</v>
       </c>
       <c r="R106" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>8.796492928534685e-05</v>
+        <v>0.0002535352078726766</v>
       </c>
       <c r="R107" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>0.000109061046840753</v>
+        <v>0.0001335362312275813</v>
       </c>
       <c r="R108" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>5.381085929856091e-05</v>
+        <v>2.364919361447701e-05</v>
       </c>
       <c r="R109" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>4.718480638698533e-05</v>
+        <v>3.065864614048908e-05</v>
       </c>
       <c r="R110" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>5.006117756097003e-05</v>
+        <v>8.750369419589046e-05</v>
       </c>
       <c r="R111" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>9.102126286026025e-05</v>
+        <v>6.77859465199248e-05</v>
       </c>
       <c r="R112" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>9.102126286026025e-05</v>
+        <v>6.77859465199248e-05</v>
       </c>
       <c r="R113" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>8.420216558054727e-05</v>
+        <v>8.147542380055795e-05</v>
       </c>
       <c r="R114" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -8044,10 +8044,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>8.143596759787999e-05</v>
+        <v>7.404708402321095e-05</v>
       </c>
       <c r="R115" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>5.638394076867358e-05</v>
+        <v>2.92491330204118e-05</v>
       </c>
       <c r="R116" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>4.288311597334154e-05</v>
+        <v>7.046842699787623e-05</v>
       </c>
       <c r="R117" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8242,10 +8242,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>4.219475010183002e-05</v>
+        <v>6.85516391348278e-05</v>
       </c>
       <c r="R118" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>5.510556497067327e-05</v>
+        <v>0.0001208751977192116</v>
       </c>
       <c r="R119" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>0.001118620023890901</v>
+        <v>0.004347424273095265</v>
       </c>
       <c r="R120" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>5.563293889636511e-05</v>
+        <v>2.747092441224604e-05</v>
       </c>
       <c r="R121" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>5.563293889636511e-05</v>
+        <v>2.747092441224604e-05</v>
       </c>
       <c r="R122" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8572,10 +8572,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>5.679779963910266e-05</v>
+        <v>8.01070949742774e-05</v>
       </c>
       <c r="R123" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>6.50328033649133e-05</v>
+        <v>4.808951040438988e-05</v>
       </c>
       <c r="R124" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>7.354666188407584e-05</v>
+        <v>6.35175726451361e-05</v>
       </c>
       <c r="R125" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>0.001083665509022183</v>
+        <v>0.00296051122933213</v>
       </c>
       <c r="R126" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>6.290184563290585e-05</v>
+        <v>7.811413270474005e-05</v>
       </c>
       <c r="R127" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>4.625794754378257e-05</v>
+        <v>5.519501012632089e-05</v>
       </c>
       <c r="R128" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>4.784601037275509e-05</v>
+        <v>0.0001272144790375923</v>
       </c>
       <c r="R129" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>6.329260765730288e-05</v>
+        <v>7.09816434634264e-05</v>
       </c>
       <c r="R130" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -9100,10 +9100,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>6.04407600281573e-05</v>
+        <v>2.026616616218175e-05</v>
       </c>
       <c r="R131" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>5.35921199285556e-05</v>
+        <v>1.985802002136704e-05</v>
       </c>
       <c r="R132" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>4.022084030433136e-05</v>
+        <v>7.243817773331309e-05</v>
       </c>
       <c r="R133" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>4.918131052440579e-05</v>
+        <v>1.819793048902633e-05</v>
       </c>
       <c r="R134" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>6.966449085870265e-05</v>
+        <v>4.084252568731607e-05</v>
       </c>
       <c r="R135" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>0.0001322188005229374</v>
+        <v>9.204246770835209e-05</v>
       </c>
       <c r="R136" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>0.0001322189008228614</v>
+        <v>9.204231156473935e-05</v>
       </c>
       <c r="R137" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>0.0001395185846263821</v>
+        <v>0.0002779491020835729</v>
       </c>
       <c r="R138" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>5.170332595135556e-05</v>
+        <v>5.410837367386986e-05</v>
       </c>
       <c r="R139" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>4.70454089341509e-05</v>
+        <v>9.428311525268809e-06</v>
       </c>
       <c r="R140" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9760,10 +9760,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>4.594125453302378e-05</v>
+        <v>8.115384927112225e-06</v>
       </c>
       <c r="R141" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>8.905868525094072e-05</v>
+        <v>6.468922550143287e-05</v>
       </c>
       <c r="R142" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>5.214442400949391e-05</v>
+        <v>2.046974743935129e-05</v>
       </c>
       <c r="R143" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9958,10 +9958,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>3.858277014037711e-05</v>
+        <v>2.270616425495613e-05</v>
       </c>
       <c r="R144" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>3.606872213977026e-05</v>
+        <v>5.505765690904789e-05</v>
       </c>
       <c r="R145" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -10090,10 +10090,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>0.0002340896565340206</v>
+        <v>0.00020356678568625</v>
       </c>
       <c r="R146" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -10156,10 +10156,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>6.986096655577747e-05</v>
+        <v>2.725966547143889e-05</v>
       </c>
       <c r="R147" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10222,17 +10222,17 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>0.0004945996059425025</v>
+        <v>0.01144426807685073</v>
       </c>
       <c r="R148" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>✅ Normal</t>
+          <t>⚠️ Anomaly</t>
         </is>
       </c>
     </row>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>4.395620262604091e-05</v>
+        <v>1.578237742921644e-05</v>
       </c>
       <c r="R149" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>4.505920117770916e-05</v>
+        <v>2.571479177163765e-05</v>
       </c>
       <c r="R150" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>5.066270293992815e-05</v>
+        <v>4.867597138074929e-05</v>
       </c>
       <c r="R151" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S151" t="b">
         <v>0</v>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>6.858897867630342e-05</v>
+        <v>2.199819880847448e-05</v>
       </c>
       <c r="R152" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S152" t="b">
         <v>0</v>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>6.858897867630342e-05</v>
+        <v>2.199819880847448e-05</v>
       </c>
       <c r="R153" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S153" t="b">
         <v>0</v>
@@ -10618,10 +10618,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>6.669814277677595e-05</v>
+        <v>5.298151567633634e-05</v>
       </c>
       <c r="R154" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S154" t="b">
         <v>0</v>
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>3.742055903389135e-05</v>
+        <v>2.047996674605951e-05</v>
       </c>
       <c r="R155" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S155" t="b">
         <v>0</v>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>3.742055903389135e-05</v>
+        <v>2.047996674605951e-05</v>
       </c>
       <c r="R156" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S156" t="b">
         <v>0</v>
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>4.816820610764867e-05</v>
+        <v>4.321191674506629e-05</v>
       </c>
       <c r="R157" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S157" t="b">
         <v>0</v>
@@ -10882,10 +10882,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>5.529906265315145e-05</v>
+        <v>3.909080906604062e-05</v>
       </c>
       <c r="R158" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S158" t="b">
         <v>0</v>
@@ -10948,10 +10948,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>0.0001056579636192658</v>
+        <v>7.248079002321941e-05</v>
       </c>
       <c r="R159" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S159" t="b">
         <v>0</v>
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>6.593808698521568e-05</v>
+        <v>3.413950420390968e-05</v>
       </c>
       <c r="R160" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S160" t="b">
         <v>0</v>
@@ -11080,10 +11080,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>8.123811156771939e-05</v>
+        <v>0.0001006024524764793</v>
       </c>
       <c r="R161" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S161" t="b">
         <v>0</v>
@@ -11146,10 +11146,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>4.359954016990005e-05</v>
+        <v>6.781895231507698e-05</v>
       </c>
       <c r="R162" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S162" t="b">
         <v>0</v>
@@ -11212,10 +11212,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>4.059409246797011e-05</v>
+        <v>2.102114262832602e-05</v>
       </c>
       <c r="R163" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S163" t="b">
         <v>0</v>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>6.622397875766242e-05</v>
+        <v>0.0001051750874589409</v>
       </c>
       <c r="R164" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S164" t="b">
         <v>0</v>
@@ -11344,10 +11344,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>7.330114779857821e-05</v>
+        <v>0.0001487790627009102</v>
       </c>
       <c r="R165" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S165" t="b">
         <v>0</v>
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>5.925373271692334e-05</v>
+        <v>3.04374395502322e-05</v>
       </c>
       <c r="R166" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S166" t="b">
         <v>0</v>
@@ -11476,10 +11476,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>4.553185994015261e-05</v>
+        <v>5.946005319414228e-05</v>
       </c>
       <c r="R167" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S167" t="b">
         <v>0</v>
@@ -11542,10 +11542,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>3.746019863799699e-05</v>
+        <v>2.648225943230478e-05</v>
       </c>
       <c r="R168" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S168" t="b">
         <v>0</v>
@@ -11608,10 +11608,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>3.996272641605609e-05</v>
+        <v>3.193684001180358e-05</v>
       </c>
       <c r="R169" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S169" t="b">
         <v>0</v>
@@ -11674,10 +11674,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>5.699185257119693e-05</v>
+        <v>3.730240127867506e-05</v>
       </c>
       <c r="R170" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S170" t="b">
         <v>0</v>
@@ -11740,10 +11740,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>5.530020963111133e-05</v>
+        <v>3.731282749370841e-05</v>
       </c>
       <c r="R171" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S171" t="b">
         <v>0</v>
@@ -11806,10 +11806,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>7.005168487261875e-05</v>
+        <v>3.299632839065508e-05</v>
       </c>
       <c r="R172" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S172" t="b">
         <v>0</v>
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>4.518545126879049e-05</v>
+        <v>1.83268121383477e-05</v>
       </c>
       <c r="R173" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S173" t="b">
         <v>0</v>
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>3.708314994178098e-05</v>
+        <v>1.690392139678563e-05</v>
       </c>
       <c r="R174" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S174" t="b">
         <v>0</v>
@@ -12004,10 +12004,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>4.696668769862695e-05</v>
+        <v>2.402993580769612e-05</v>
       </c>
       <c r="R175" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S175" t="b">
         <v>0</v>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>5.817082549717244e-05</v>
+        <v>7.562527925901327e-05</v>
       </c>
       <c r="R176" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S176" t="b">
         <v>0</v>
@@ -12136,10 +12136,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>5.817082549717244e-05</v>
+        <v>7.562527925901327e-05</v>
       </c>
       <c r="R177" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S177" t="b">
         <v>0</v>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>0.0001128604777223931</v>
+        <v>6.787769373560824e-05</v>
       </c>
       <c r="R178" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S178" t="b">
         <v>0</v>
@@ -12268,10 +12268,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>6.44159073169705e-05</v>
+        <v>4.600233780638116e-05</v>
       </c>
       <c r="R179" t="n">
-        <v>0.001352842468665255</v>
+        <v>0.005200238997286627</v>
       </c>
       <c r="S179" t="b">
         <v>0</v>
